--- a/results/class_sensitivity/prism_hsp90_class_sensitivity.xlsx
+++ b/results/class_sensitivity/prism_hsp90_class_sensitivity.xlsx
@@ -655,10 +655,10 @@
         <v>-0.1786272139903385</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>0.3076923076923077</v>
+        <v>0.3205128205128205</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -689,10 +689,10 @@
         <v>-0.2094323762561981</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>0.6666666666666666</v>
+        <v>0.6499999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -740,7 +740,7 @@
         <v>-0.1799067898613997</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>0.5714285714285714</v>
@@ -757,10 +757,10 @@
         <v>-0.2183080445642374</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E8">
-        <v>0.6793381037567083</v>
+        <v>0.6279069767441861</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -774,10 +774,10 @@
         <v>-0.1662653967408163</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E9">
-        <v>0.6</v>
+        <v>0.5391472868217054</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -842,10 +842,10 @@
         <v>-0.2235656201793519</v>
       </c>
       <c r="D13">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E13">
-        <v>0.7897435897435897</v>
+        <v>0.7333333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -859,10 +859,10 @@
         <v>-0.2064610311547386</v>
       </c>
       <c r="D14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E14">
-        <v>0.7441860465116279</v>
+        <v>0.772093023255814</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -876,10 +876,10 @@
         <v>-0.2082082076743421</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E15">
-        <v>0.2583333333333333</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -927,10 +927,10 @@
         <v>-0.1414054398988475</v>
       </c>
       <c r="D18">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E18">
-        <v>0.6976744186046512</v>
+        <v>0.7626303127506014</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -944,10 +944,10 @@
         <v>-0.1783653544666676</v>
       </c>
       <c r="D19">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E19">
-        <v>0.7666666666666667</v>
+        <v>0.7404761904761905</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -961,10 +961,10 @@
         <v>-0.2272999068630794</v>
       </c>
       <c r="D20">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E20">
-        <v>0.2142857142857143</v>
+        <v>0.2562015503875969</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -978,7 +978,7 @@
         <v>-0.2027319592747009</v>
       </c>
       <c r="D21">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E21">
         <v>0.4418604651162791</v>
@@ -995,10 +995,10 @@
         <v>-0.2357862821744499</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E22">
-        <v>0.1162790697674419</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1012,10 +1012,10 @@
         <v>-0.1928960493937777</v>
       </c>
       <c r="D23">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E23">
-        <v>0.4523809523809524</v>
+        <v>0.296551724137931</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1029,10 +1029,10 @@
         <v>-0.1891070006869582</v>
       </c>
       <c r="D24">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E24">
-        <v>0.6923076923076923</v>
+        <v>0.6252236135957066</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1046,10 +1046,10 @@
         <v>-0.1679123265606992</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E25">
-        <v>0.7690476190476191</v>
+        <v>0.6511627906976745</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1077,10 +1077,10 @@
         <v>-0.2002121226750436</v>
       </c>
       <c r="D27">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E27">
-        <v>0.4666666666666667</v>
+        <v>0.4775193798449612</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1094,7 +1094,7 @@
         <v>-0.2539667075870732</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E28">
         <v>0.2</v>
@@ -1111,10 +1111,10 @@
         <v>-0.1820048265378515</v>
       </c>
       <c r="D29">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E29">
-        <v>0.1785714285714286</v>
+        <v>0.1726190476190476</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1145,10 +1145,10 @@
         <v>-0.1998464016445489</v>
       </c>
       <c r="D31">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E31">
-        <v>0.3928571428571428</v>
+        <v>0.3964285714285715</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1162,10 +1162,10 @@
         <v>-0.205184187788136</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E32">
-        <v>0.8023255813953489</v>
+        <v>0.7666666666666667</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1179,10 +1179,10 @@
         <v>-0.184285453771279</v>
       </c>
       <c r="D33">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E33">
-        <v>0.7857142857142857</v>
+        <v>0.7998338870431894</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1196,10 +1196,10 @@
         <v>-0.194595351118395</v>
       </c>
       <c r="D34">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E34">
-        <v>0.2452934662236988</v>
+        <v>0.2884615384615384</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1213,7 +1213,7 @@
         <v>-0.2238031966272546</v>
       </c>
       <c r="D35">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E35">
         <v>0.2093023255813954</v>
@@ -1230,10 +1230,10 @@
         <v>-0.226134911817538</v>
       </c>
       <c r="D36">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E36">
-        <v>0.8418604651162791</v>
+        <v>0.9615384615384616</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1247,10 +1247,10 @@
         <v>-0.222738672149269</v>
       </c>
       <c r="D37">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E37">
-        <v>0.1904761904761905</v>
+        <v>0.2870879120879121</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1298,10 +1298,10 @@
         <v>-0.2418526659406501</v>
       </c>
       <c r="D40">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E40">
-        <v>0.1333333333333333</v>
+        <v>0.2012820512820513</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1332,10 +1332,10 @@
         <v>-0.2392060740558485</v>
       </c>
       <c r="D42">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E42">
-        <v>0.7</v>
+        <v>0.643103448275862</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1349,10 +1349,10 @@
         <v>-0.2246998597349494</v>
       </c>
       <c r="D43">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E43">
-        <v>0.5952380952380952</v>
+        <v>0.692970822281167</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1383,10 +1383,10 @@
         <v>-0.1611385731101388</v>
       </c>
       <c r="D45">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E45">
-        <v>0.8</v>
+        <v>0.8069767441860465</v>
       </c>
     </row>
   </sheetData>

--- a/results/class_sensitivity/prism_hsp90_class_sensitivity.xlsx
+++ b/results/class_sensitivity/prism_hsp90_class_sensitivity.xlsx
@@ -655,10 +655,10 @@
         <v>-0.1786272139903385</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>0.3205128205128205</v>
+        <v>0.2701252236135957</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -689,10 +689,10 @@
         <v>-0.2094323762561981</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E4">
-        <v>0.6499999999999999</v>
+        <v>0.6821705426356589</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -740,7 +740,7 @@
         <v>-0.1799067898613997</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E7">
         <v>0.5714285714285714</v>
@@ -757,10 +757,10 @@
         <v>-0.2183080445642374</v>
       </c>
       <c r="D8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E8">
-        <v>0.6279069767441861</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -774,10 +774,10 @@
         <v>-0.1662653967408163</v>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E9">
-        <v>0.5391472868217054</v>
+        <v>0.5833333333333333</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -842,7 +842,7 @@
         <v>-0.2235656201793519</v>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E13">
         <v>0.7333333333333333</v>
@@ -859,7 +859,7 @@
         <v>-0.2064610311547386</v>
       </c>
       <c r="D14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E14">
         <v>0.772093023255814</v>
@@ -876,10 +876,10 @@
         <v>-0.2082082076743421</v>
       </c>
       <c r="D15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E15">
-        <v>0.3</v>
+        <v>0.2666666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -927,10 +927,10 @@
         <v>-0.1414054398988475</v>
       </c>
       <c r="D18">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E18">
-        <v>0.7626303127506014</v>
+        <v>0.7655038759689923</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -944,10 +944,10 @@
         <v>-0.1783653544666676</v>
       </c>
       <c r="D19">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E19">
-        <v>0.7404761904761905</v>
+        <v>0.7670542635658915</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -961,10 +961,10 @@
         <v>-0.2272999068630794</v>
       </c>
       <c r="D20">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E20">
-        <v>0.2562015503875969</v>
+        <v>0.2238095238095238</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -978,10 +978,10 @@
         <v>-0.2027319592747009</v>
       </c>
       <c r="D21">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21">
-        <v>0.4418604651162791</v>
+        <v>0.5116279069767442</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -995,10 +995,10 @@
         <v>-0.2357862821744499</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22">
-        <v>0.2</v>
+        <v>0.1581395348837209</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1012,10 +1012,10 @@
         <v>-0.1928960493937777</v>
       </c>
       <c r="D23">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E23">
-        <v>0.296551724137931</v>
+        <v>0.3761904761904762</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1029,7 +1029,7 @@
         <v>-0.1891070006869582</v>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E24">
         <v>0.6252236135957066</v>
@@ -1046,10 +1046,10 @@
         <v>-0.1679123265606992</v>
       </c>
       <c r="D25">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E25">
-        <v>0.6511627906976745</v>
+        <v>0.7380952380952381</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1077,10 +1077,10 @@
         <v>-0.2002121226750436</v>
       </c>
       <c r="D27">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E27">
-        <v>0.4775193798449612</v>
+        <v>0.4666666666666667</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1094,7 +1094,7 @@
         <v>-0.2539667075870732</v>
       </c>
       <c r="D28">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E28">
         <v>0.2</v>
@@ -1145,7 +1145,7 @@
         <v>-0.1998464016445489</v>
       </c>
       <c r="D31">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E31">
         <v>0.3964285714285715</v>
@@ -1162,10 +1162,10 @@
         <v>-0.205184187788136</v>
       </c>
       <c r="D32">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E32">
-        <v>0.7666666666666667</v>
+        <v>0.7674418604651163</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1179,10 +1179,10 @@
         <v>-0.184285453771279</v>
       </c>
       <c r="D33">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E33">
-        <v>0.7998338870431894</v>
+        <v>0.7761904761904762</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1196,10 +1196,10 @@
         <v>-0.194595351118395</v>
       </c>
       <c r="D34">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E34">
-        <v>0.2884615384615384</v>
+        <v>0.2666666666666667</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1213,10 +1213,10 @@
         <v>-0.2238031966272546</v>
       </c>
       <c r="D35">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E35">
-        <v>0.2093023255813954</v>
+        <v>0.2008050089445438</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1230,10 +1230,10 @@
         <v>-0.226134911817538</v>
       </c>
       <c r="D36">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E36">
-        <v>0.9615384615384616</v>
+        <v>0.8837209302325582</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1247,10 +1247,10 @@
         <v>-0.222738672149269</v>
       </c>
       <c r="D37">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E37">
-        <v>0.2870879120879121</v>
+        <v>0.2380952380952381</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1298,10 +1298,10 @@
         <v>-0.2418526659406501</v>
       </c>
       <c r="D40">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E40">
-        <v>0.2012820512820513</v>
+        <v>0.1333333333333333</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1332,10 +1332,10 @@
         <v>-0.2392060740558485</v>
       </c>
       <c r="D42">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E42">
-        <v>0.643103448275862</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1349,10 +1349,10 @@
         <v>-0.2246998597349494</v>
       </c>
       <c r="D43">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E43">
-        <v>0.692970822281167</v>
+        <v>0.680952380952381</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1383,7 +1383,7 @@
         <v>-0.1611385731101388</v>
       </c>
       <c r="D45">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E45">
         <v>0.8069767441860465</v>
